--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8581,0.0508,0.0858,0.0048</t>
-  </si>
-  <si>
-    <t>0.7681,0.0444,0.0740,0.0328</t>
-  </si>
-  <si>
-    <t>0.8463,0.0402,0.0894,0.0047</t>
-  </si>
-  <si>
-    <t>0.7655,0.1019,0.0520,0.0131</t>
-  </si>
-  <si>
-    <t>0.8043,0.0623,0.0475,0.0153</t>
-  </si>
-  <si>
-    <t>0.7350,0.1936,0.0407,0.0050</t>
-  </si>
-  <si>
-    <t>0.6063,0.2494,0.1343,0.0163</t>
-  </si>
-  <si>
-    <t>0.6455,0.1472,0.0551,0.0257</t>
-  </si>
-  <si>
-    <t>0.7193,0.1460,0.0781,0.0136</t>
-  </si>
-  <si>
-    <t>0.7313,0.1230,0.0599,0.0132</t>
-  </si>
-  <si>
-    <t>0.7932,0.0928,0.0545,0.0113</t>
-  </si>
-  <si>
-    <t>0.7265,0.1037,0.0306,0.0217</t>
-  </si>
-  <si>
-    <t>0.9309,0.0128,0.0678,0.0003</t>
-  </si>
-  <si>
-    <t>0.9557,0.0071,0.0309,0.0003</t>
-  </si>
-  <si>
-    <t>0.8602,0.0359,0.1144,0.0008</t>
-  </si>
-  <si>
-    <t>0.8531,0.0462,0.0899,0.0009</t>
-  </si>
-  <si>
-    <t>0.8506,0.0662,0.0599,0.0029</t>
-  </si>
-  <si>
-    <t>0.4016,0.6714,0.0719,0.0027</t>
-  </si>
-  <si>
-    <t>0.5327,0.5047,0.0786,0.0021</t>
-  </si>
-  <si>
-    <t>0.6770,0.2752,0.0721,0.0055</t>
-  </si>
-  <si>
-    <t>0.2795,0.7561,0.1174,0.0043</t>
-  </si>
-  <si>
-    <t>0.2890,0.7680,0.0955,0.0025</t>
-  </si>
-  <si>
-    <t>0.9256,0.0072,0.0784,0.0003</t>
-  </si>
-  <si>
-    <t>0.8720,0.0217,0.1221,0.0016</t>
-  </si>
-  <si>
-    <t>0.8628,0.0145,0.1382,0.0007</t>
-  </si>
-  <si>
-    <t>0.9491,0.0093,0.0425,0.0001</t>
-  </si>
-  <si>
-    <t>0.9671,0.0037,0.0282,0.0001</t>
-  </si>
-  <si>
-    <t>0.8119,0.0072,0.2756,0.0010</t>
-  </si>
-  <si>
-    <t>0.5834,0.0247,0.5651,0.0035</t>
-  </si>
-  <si>
-    <t>0.8559,0.0923,0.0479,0.0022</t>
-  </si>
-  <si>
-    <t>0.8734,0.0811,0.0328,0.0022</t>
-  </si>
-  <si>
-    <t>0.0329,0.1119,0.9691,0.0029</t>
-  </si>
-  <si>
-    <t>0.4933,0.4082,0.1963,0.0015</t>
-  </si>
-  <si>
-    <t>0.8686,0.0514,0.0332,0.0029</t>
-  </si>
-  <si>
-    <t>0.8917,0.0284,0.0575,0.0028</t>
-  </si>
-  <si>
-    <t>0.7980,0.1405,0.0485,0.0041</t>
-  </si>
-  <si>
-    <t>0.8013,0.1310,0.0422,0.0022</t>
-  </si>
-  <si>
-    <t>0.5724,0.2644,0.0423,0.0011</t>
-  </si>
-  <si>
-    <t>0.9126,0.0051,0.0735,0.0006</t>
-  </si>
-  <si>
-    <t>0.9356,0.0032,0.0728,0.0003</t>
-  </si>
-  <si>
-    <t>0.9105,0.0070,0.0874,0.0006</t>
-  </si>
-  <si>
-    <t>0.9366,0.0029,0.1065,0.0001</t>
-  </si>
-  <si>
-    <t>0.6476,0.2574,0.1152,0.0039</t>
-  </si>
-  <si>
-    <t>0.7006,0.0217,0.3923,0.0013</t>
-  </si>
-  <si>
-    <t>0.5901,0.3447,0.0650,0.0116</t>
-  </si>
-  <si>
-    <t>0.8074,0.1907,0.0354,0.0012</t>
-  </si>
-  <si>
-    <t>0.1605,0.8967,0.0436,0.0023</t>
-  </si>
-  <si>
-    <t>0.4075,0.6935,0.0445,0.0007</t>
-  </si>
-  <si>
-    <t>0.5892,0.0465,0.4162,0.0023</t>
-  </si>
-  <si>
-    <t>0.5641,0.0135,0.5728,0.0016</t>
-  </si>
-  <si>
-    <t>0.9457,0.0037,0.0689,0.0002</t>
-  </si>
-  <si>
-    <t>0.8902,0.0150,0.1225,0.0005</t>
-  </si>
-  <si>
-    <t>0.5763,0.0450,0.5165,0.0018</t>
-  </si>
-  <si>
-    <t>0.8116,0.0289,0.1906,0.0003</t>
-  </si>
-  <si>
-    <t>0.7598,0.1411,0.0890,0.0064</t>
-  </si>
-  <si>
-    <t>0.7793,0.1509,0.0521,0.0049</t>
-  </si>
-  <si>
-    <t>0.8040,0.0319,0.0294,0.0262</t>
-  </si>
-  <si>
-    <t>0.3877,0.2132,0.6309,0.0073</t>
-  </si>
-  <si>
-    <t>0.8103,0.0579,0.0398,0.0122</t>
-  </si>
-  <si>
-    <t>0.7889,0.0657,0.0472,0.0207</t>
-  </si>
-  <si>
-    <t>0.5708,0.3464,0.0788,0.0111</t>
-  </si>
-  <si>
-    <t>0.7754,0.0688,0.1775,0.0006</t>
-  </si>
-  <si>
-    <t>0.5879,0.0104,0.6317,0.0005</t>
-  </si>
-  <si>
-    <t>0.7645,0.0102,0.3798,0.0006</t>
-  </si>
-  <si>
-    <t>0.7272,0.0566,0.1737,0.0003</t>
-  </si>
-  <si>
-    <t>0.5517,0.0215,0.5740,0.0008</t>
-  </si>
-  <si>
-    <t>0.7456,0.1708,0.1052,0.0022</t>
-  </si>
-  <si>
-    <t>0.0022,0.9967,0.0099,0.0004</t>
-  </si>
-  <si>
-    <t>0.9277,0.0257,0.0268,0.0012</t>
-  </si>
-  <si>
-    <t>0.8921,0.0527,0.0310,0.0011</t>
-  </si>
-  <si>
-    <t>0.3834,0.1937,0.5587,0.0052</t>
-  </si>
-  <si>
-    <t>0.2734,0.6135,0.1462,0.0006</t>
-  </si>
-  <si>
-    <t>0.8879,0.0178,0.1035,0.0002</t>
-  </si>
-  <si>
-    <t>0.4885,0.3749,0.0542,0.0003</t>
-  </si>
-  <si>
-    <t>0.4151,0.4738,0.1304,0.0003</t>
-  </si>
-  <si>
-    <t>0.8714,0.0356,0.0619,0.0031</t>
-  </si>
-  <si>
-    <t>0.8390,0.0395,0.0713,0.0093</t>
-  </si>
-  <si>
-    <t>0.9299,0.0181,0.0134,0.0032</t>
-  </si>
-  <si>
-    <t>0.9638,0.0152,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.6781,0.1552,0.0736,0.0314</t>
-  </si>
-  <si>
-    <t>0.8972,0.0261,0.0229,0.0068</t>
-  </si>
-  <si>
-    <t>0.3714,0.4491,0.2028,0.0010</t>
-  </si>
-  <si>
-    <t>0.6577,0.0258,0.4379,0.0005</t>
-  </si>
-  <si>
-    <t>0.6820,0.0244,0.3718,0.0006</t>
-  </si>
-  <si>
-    <t>0.8168,0.0318,0.1306,0.0005</t>
-  </si>
-  <si>
-    <t>0.7276,0.1117,0.1128,0.0003</t>
-  </si>
-  <si>
-    <t>0.5924,0.1074,0.2135,0.0005</t>
-  </si>
-  <si>
-    <t>0.8474,0.0475,0.0412,0.0087</t>
-  </si>
-  <si>
-    <t>0.7536,0.1492,0.0366,0.0069</t>
-  </si>
-  <si>
-    <t>0.8101,0.0854,0.0671,0.0065</t>
-  </si>
-  <si>
-    <t>0.7462,0.1229,0.0557,0.0192</t>
-  </si>
-  <si>
-    <t>0.8257,0.0720,0.0334,0.0111</t>
-  </si>
-  <si>
-    <t>0.6511,0.1270,0.0444,0.0364</t>
-  </si>
-  <si>
-    <t>0.7606,0.0588,0.0245,0.0305</t>
-  </si>
-  <si>
-    <t>0.8283,0.0553,0.0484,0.0152</t>
-  </si>
-  <si>
-    <t>0.8391,0.0672,0.0397,0.0059</t>
-  </si>
-  <si>
-    <t>0.8342,0.0602,0.0320,0.0145</t>
-  </si>
-  <si>
-    <t>0.7414,0.1078,0.0477,0.0173</t>
-  </si>
-  <si>
-    <t>0.7261,0.1282,0.0783,0.0179</t>
-  </si>
-  <si>
-    <t>0.8100,0.0796,0.0361,0.0122</t>
-  </si>
-  <si>
-    <t>0.8456,0.0725,0.0439,0.0058</t>
-  </si>
-  <si>
-    <t>0.7650,0.1053,0.0391,0.0175</t>
-  </si>
-  <si>
-    <t>0.7474,0.0647,0.0315,0.0293</t>
-  </si>
-  <si>
-    <t>0.1119,0.1215,0.9053,0.0028</t>
-  </si>
-  <si>
-    <t>0.8315,0.0123,0.2238,0.0006</t>
-  </si>
-  <si>
-    <t>0.7886,0.0676,0.0730,0.0119</t>
-  </si>
-  <si>
-    <t>0.6628,0.0316,0.3617,0.0009</t>
-  </si>
-  <si>
-    <t>0.5889,0.3448,0.1384,0.0052</t>
-  </si>
-  <si>
-    <t>0.3895,0.6659,0.0726,0.0019</t>
-  </si>
-  <si>
-    <t>0.6014,0.3632,0.1184,0.0068</t>
-  </si>
-  <si>
-    <t>0.3631,0.6570,0.0693,0.0068</t>
-  </si>
-  <si>
-    <t>0.6084,0.3660,0.0864,0.0045</t>
-  </si>
-  <si>
-    <t>0.2156,0.8093,0.0917,0.0027</t>
-  </si>
-  <si>
-    <t>0.5539,0.4860,0.0884,0.0035</t>
-  </si>
-  <si>
-    <t>0.8328,0.0962,0.0704,0.0014</t>
-  </si>
-  <si>
-    <t>0.8192,0.0377,0.1807,0.0008</t>
-  </si>
-  <si>
-    <t>0.8860,0.0621,0.0438,0.0008</t>
-  </si>
-  <si>
-    <t>0.9151,0.0249,0.0509,0.0007</t>
-  </si>
-  <si>
-    <t>0.8449,0.0365,0.1115,0.0032</t>
-  </si>
-  <si>
-    <t>0.8282,0.1742,0.0245,0.0009</t>
-  </si>
-  <si>
-    <t>0.7434,0.2779,0.0490,0.0016</t>
-  </si>
-  <si>
-    <t>0.8909,0.0530,0.0373,0.0016</t>
-  </si>
-  <si>
-    <t>0.0475,0.9564,0.0877,0.0021</t>
-  </si>
-  <si>
-    <t>0.8359,0.1437,0.0302,0.0010</t>
-  </si>
-  <si>
-    <t>0.8387,0.1285,0.0318,0.0017</t>
-  </si>
-  <si>
-    <t>0.8247,0.1261,0.0674,0.0024</t>
-  </si>
-  <si>
-    <t>0.7822,0.1718,0.0427,0.0043</t>
-  </si>
-  <si>
-    <t>0.8002,0.0767,0.0717,0.0086</t>
-  </si>
-  <si>
-    <t>0.8440,0.0513,0.0677,0.0052</t>
-  </si>
-  <si>
-    <t>0.7019,0.1728,0.0778,0.0179</t>
-  </si>
-  <si>
-    <t>0.7512,0.1097,0.0478,0.0190</t>
-  </si>
-  <si>
-    <t>0.8077,0.0767,0.0715,0.0054</t>
-  </si>
-  <si>
-    <t>0.6238,0.1659,0.0351,0.0329</t>
-  </si>
-  <si>
-    <t>0.7681,0.0869,0.0589,0.0101</t>
-  </si>
-  <si>
-    <t>0.9390,0.0070,0.0720,0.0001</t>
-  </si>
-  <si>
-    <t>0.7142,0.0746,0.1406,0.0006</t>
-  </si>
-  <si>
-    <t>0.8253,0.0377,0.1245,0.0015</t>
-  </si>
-  <si>
-    <t>0.9037,0.0084,0.1017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9153,0.0165,0.0694,0.0004</t>
-  </si>
-  <si>
-    <t>0.8800,0.0376,0.0715,0.0020</t>
-  </si>
-  <si>
-    <t>0.8345,0.0178,0.2317,0.0006</t>
-  </si>
-  <si>
-    <t>0.9084,0.0235,0.0526,0.0016</t>
-  </si>
-  <si>
-    <t>0.8657,0.0193,0.0413,0.0134</t>
-  </si>
-  <si>
-    <t>0.9071,0.0149,0.0269,0.0052</t>
-  </si>
-  <si>
-    <t>0.9585,0.0088,0.0128,0.0010</t>
-  </si>
-  <si>
-    <t>0.8143,0.0556,0.0699,0.0084</t>
-  </si>
-  <si>
-    <t>0.2041,0.5046,0.4804,0.0063</t>
-  </si>
-  <si>
-    <t>0.6715,0.2001,0.0389,0.0138</t>
-  </si>
-  <si>
-    <t>0.8544,0.0564,0.0445,0.0046</t>
-  </si>
-  <si>
-    <t>0.7608,0.0674,0.0874,0.0234</t>
-  </si>
-  <si>
-    <t>0.7667,0.1475,0.0797,0.0062</t>
-  </si>
-  <si>
-    <t>0.8092,0.0979,0.0754,0.0052</t>
-  </si>
-  <si>
-    <t>0.7964,0.0902,0.0944,0.0056</t>
-  </si>
-  <si>
-    <t>0.6920,0.1271,0.0856,0.0213</t>
-  </si>
-  <si>
-    <t>0.0764,0.4337,0.8690,0.0158</t>
-  </si>
-  <si>
-    <t>0.8566,0.0589,0.0286,0.0085</t>
-  </si>
-  <si>
-    <t>0.7886,0.1032,0.0609,0.0070</t>
-  </si>
-  <si>
-    <t>0.6212,0.4338,0.0674,0.0043</t>
-  </si>
-  <si>
-    <t>0.8918,0.0632,0.0385,0.0008</t>
-  </si>
-  <si>
-    <t>0.8404,0.0509,0.0365,0.0133</t>
-  </si>
-  <si>
-    <t>0.7752,0.1454,0.0802,0.0025</t>
-  </si>
-  <si>
-    <t>0.8979,0.0591,0.0373,0.0009</t>
-  </si>
-  <si>
-    <t>0.8569,0.0884,0.0550,0.0023</t>
-  </si>
-  <si>
-    <t>0.7303,0.1178,0.0468,0.0155</t>
-  </si>
-  <si>
-    <t>0.7734,0.0631,0.0230,0.0215</t>
-  </si>
-  <si>
-    <t>0.8063,0.0733,0.0327,0.0147</t>
-  </si>
-  <si>
-    <t>0.8906,0.0321,0.0323,0.0068</t>
-  </si>
-  <si>
-    <t>0.7921,0.1100,0.0615,0.0059</t>
-  </si>
-  <si>
-    <t>0.8608,0.0539,0.0379,0.0050</t>
-  </si>
-  <si>
-    <t>0.7995,0.1170,0.0620,0.0065</t>
-  </si>
-  <si>
-    <t>0.7141,0.1442,0.0695,0.0126</t>
-  </si>
-  <si>
-    <t>0.7701,0.1251,0.0800,0.0078</t>
-  </si>
-  <si>
-    <t>0.7190,0.1700,0.0591,0.0110</t>
-  </si>
-  <si>
-    <t>0.7783,0.1474,0.0734,0.0046</t>
-  </si>
-  <si>
-    <t>0.7479,0.1140,0.0411,0.0095</t>
-  </si>
-  <si>
-    <t>0.8780,0.0507,0.0366,0.0040</t>
-  </si>
-  <si>
-    <t>0.6762,0.1705,0.0478,0.0144</t>
-  </si>
-  <si>
-    <t>0.8280,0.0223,0.0507,0.0204</t>
-  </si>
-  <si>
-    <t>0.7949,0.0766,0.0519,0.0136</t>
-  </si>
-  <si>
-    <t>0.4681,0.0448,0.6795,0.0019</t>
-  </si>
-  <si>
-    <t>0.7885,0.0947,0.0810,0.0087</t>
-  </si>
-  <si>
-    <t>0.7113,0.0267,0.3621,0.0009</t>
-  </si>
-  <si>
-    <t>0.7773,0.0081,0.3144,0.0005</t>
-  </si>
-  <si>
-    <t>0.8562,0.0454,0.1047,0.0003</t>
-  </si>
-  <si>
-    <t>0.3437,0.0615,0.6650,0.0014</t>
-  </si>
-  <si>
-    <t>0.7816,0.0174,0.2552,0.0003</t>
-  </si>
-  <si>
-    <t>0.7194,0.0118,0.4353,0.0002</t>
-  </si>
-  <si>
-    <t>0.8531,0.0076,0.2128,0.0001</t>
-  </si>
-  <si>
-    <t>0.8452,0.0644,0.0653,0.0023</t>
-  </si>
-  <si>
-    <t>0.8534,0.0400,0.1031,0.0014</t>
-  </si>
-  <si>
-    <t>0.8507,0.0401,0.1098,0.0008</t>
-  </si>
-  <si>
-    <t>0.6417,0.3123,0.1394,0.0027</t>
-  </si>
-  <si>
-    <t>0.9024,0.0418,0.0518,0.0005</t>
-  </si>
-  <si>
-    <t>0.9242,0.0184,0.0436,0.0006</t>
-  </si>
-  <si>
-    <t>0.8699,0.0692,0.0374,0.0057</t>
-  </si>
-  <si>
-    <t>0.8658,0.0534,0.0660,0.0008</t>
-  </si>
-  <si>
-    <t>0.6787,0.2253,0.1279,0.0091</t>
-  </si>
-  <si>
-    <t>0.6239,0.1894,0.0798,0.0235</t>
-  </si>
-  <si>
-    <t>0.7149,0.1630,0.0673,0.0122</t>
-  </si>
-  <si>
-    <t>0.6199,0.1932,0.0777,0.0227</t>
-  </si>
-  <si>
-    <t>0.6039,0.2405,0.0981,0.0212</t>
-  </si>
-  <si>
-    <t>0.8884,0.0459,0.0491,0.0013</t>
-  </si>
-  <si>
-    <t>0.9097,0.0147,0.1026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9106,0.0297,0.0551,0.0007</t>
-  </si>
-  <si>
-    <t>0.9648,0.0039,0.0380,0.0002</t>
-  </si>
-  <si>
-    <t>0.8714,0.0478,0.0645,0.0011</t>
-  </si>
-  <si>
-    <t>0.6416,0.0829,0.3403,0.0026</t>
-  </si>
-  <si>
-    <t>0.8840,0.0058,0.1469,0.0009</t>
-  </si>
-  <si>
-    <t>0.8488,0.0077,0.1875,0.0003</t>
-  </si>
-  <si>
-    <t>0.7861,0.0104,0.2991,0.0005</t>
-  </si>
-  <si>
-    <t>0.8405,0.0237,0.1521,0.0010</t>
-  </si>
-  <si>
-    <t>0.8087,0.0948,0.0548,0.0082</t>
-  </si>
-  <si>
-    <t>0.7432,0.0901,0.0825,0.0196</t>
-  </si>
-  <si>
-    <t>0.7704,0.1098,0.0389,0.0126</t>
-  </si>
-  <si>
-    <t>0.7818,0.1030,0.0425,0.0077</t>
-  </si>
-  <si>
-    <t>0.8096,0.1316,0.0571,0.0058</t>
-  </si>
-  <si>
-    <t>0.5307,0.3831,0.0954,0.0145</t>
-  </si>
-  <si>
-    <t>0.8401,0.0653,0.0526,0.0088</t>
-  </si>
-  <si>
-    <t>0.7931,0.0864,0.0445,0.0156</t>
-  </si>
-  <si>
-    <t>0.7721,0.1133,0.1213,0.0025</t>
-  </si>
-  <si>
-    <t>0.8658,0.0387,0.0624,0.0026</t>
-  </si>
-  <si>
-    <t>0.8017,0.0925,0.1238,0.0026</t>
-  </si>
-  <si>
-    <t>0.6662,0.0168,0.3711,0.0003</t>
-  </si>
-  <si>
-    <t>0.5414,0.0300,0.5395,0.0034</t>
-  </si>
-  <si>
-    <t>0.7439,0.0491,0.2183,0.0025</t>
-  </si>
-  <si>
-    <t>0.4982,0.0023,0.7641,0.0006</t>
-  </si>
-  <si>
-    <t>0.9187,0.0168,0.0578,0.0003</t>
-  </si>
-  <si>
-    <t>0.6280,0.0182,0.4408,0.0014</t>
-  </si>
-  <si>
-    <t>0.8758,0.0038,0.1718,0.0004</t>
-  </si>
-  <si>
-    <t>0.7766,0.1002,0.1200,0.0041</t>
-  </si>
-  <si>
-    <t>0.9429,0.0075,0.0445,0.0003</t>
-  </si>
-  <si>
-    <t>0.8886,0.0419,0.0556,0.0017</t>
-  </si>
-  <si>
-    <t>0.9234,0.0117,0.0670,0.0006</t>
-  </si>
-  <si>
-    <t>0.8492,0.0498,0.0241,0.0134</t>
-  </si>
-  <si>
-    <t>0.8509,0.0446,0.0344,0.0086</t>
-  </si>
-  <si>
-    <t>0.7277,0.1294,0.0389,0.0153</t>
-  </si>
-  <si>
-    <t>0.6778,0.1786,0.0519,0.0190</t>
-  </si>
-  <si>
-    <t>0.8208,0.0994,0.0521,0.0063</t>
-  </si>
-  <si>
-    <t>0.4970,0.2898,0.0687,0.0303</t>
-  </si>
-  <si>
-    <t>0.8185,0.0780,0.0341,0.0103</t>
-  </si>
-  <si>
-    <t>0.8597,0.0331,0.0219,0.0101</t>
-  </si>
-  <si>
-    <t>0.7782,0.0899,0.1093,0.0010</t>
-  </si>
-  <si>
-    <t>0.7048,0.0157,0.3482,0.0002</t>
-  </si>
-  <si>
-    <t>0.8195,0.0231,0.1979,0.0005</t>
-  </si>
-  <si>
-    <t>0.8670,0.0330,0.0945,0.0020</t>
-  </si>
-  <si>
-    <t>0.8098,0.0200,0.1989,0.0013</t>
-  </si>
-  <si>
-    <t>0.9512,0.0121,0.0276,0.0007</t>
-  </si>
-  <si>
-    <t>0.6999,0.0548,0.3077,0.0008</t>
-  </si>
-  <si>
-    <t>0.7725,0.0124,0.3124,0.0024</t>
-  </si>
-  <si>
-    <t>0.8864,0.0351,0.0288,0.0047</t>
-  </si>
-  <si>
-    <t>0.9497,0.0100,0.0178,0.0015</t>
-  </si>
-  <si>
-    <t>0.7786,0.1015,0.1122,0.0081</t>
-  </si>
-  <si>
-    <t>0.8341,0.0374,0.0597,0.0130</t>
-  </si>
-  <si>
-    <t>0.9054,0.0173,0.0346,0.0029</t>
-  </si>
-  <si>
-    <t>0.8103,0.0812,0.0876,0.0039</t>
+    <t>0.7773,0.1153,0.0752,0.0081</t>
+  </si>
+  <si>
+    <t>0.8124,0.0693,0.0430,0.0104</t>
+  </si>
+  <si>
+    <t>0.8561,0.0501,0.0393,0.0068</t>
+  </si>
+  <si>
+    <t>0.7005,0.2455,0.0468,0.0074</t>
+  </si>
+  <si>
+    <t>0.8500,0.0725,0.0451,0.0058</t>
+  </si>
+  <si>
+    <t>0.8517,0.0625,0.0471,0.0061</t>
+  </si>
+  <si>
+    <t>0.7412,0.1142,0.0476,0.0181</t>
+  </si>
+  <si>
+    <t>0.7524,0.0860,0.0450,0.0221</t>
+  </si>
+  <si>
+    <t>0.7215,0.1646,0.0516,0.0105</t>
+  </si>
+  <si>
+    <t>0.7361,0.1182,0.0468,0.0158</t>
+  </si>
+  <si>
+    <t>0.8113,0.0499,0.0255,0.0187</t>
+  </si>
+  <si>
+    <t>0.5885,0.2198,0.0430,0.0176</t>
+  </si>
+  <si>
+    <t>0.8643,0.0555,0.0818,0.0004</t>
+  </si>
+  <si>
+    <t>0.9047,0.0205,0.0775,0.0011</t>
+  </si>
+  <si>
+    <t>0.9082,0.0239,0.0607,0.0009</t>
+  </si>
+  <si>
+    <t>0.6964,0.1562,0.1594,0.0023</t>
+  </si>
+  <si>
+    <t>0.8917,0.0465,0.0431,0.0014</t>
+  </si>
+  <si>
+    <t>0.4785,0.5890,0.0868,0.0016</t>
+  </si>
+  <si>
+    <t>0.7783,0.1506,0.0608,0.0033</t>
+  </si>
+  <si>
+    <t>0.7868,0.1186,0.0859,0.0052</t>
+  </si>
+  <si>
+    <t>0.1813,0.8469,0.1308,0.0075</t>
+  </si>
+  <si>
+    <t>0.2757,0.7844,0.0883,0.0027</t>
+  </si>
+  <si>
+    <t>0.9005,0.0169,0.1119,0.0003</t>
+  </si>
+  <si>
+    <t>0.9352,0.0152,0.0464,0.0003</t>
+  </si>
+  <si>
+    <t>0.8914,0.0222,0.0635,0.0002</t>
+  </si>
+  <si>
+    <t>0.9091,0.0118,0.0741,0.0010</t>
+  </si>
+  <si>
+    <t>0.8435,0.0117,0.2138,0.0006</t>
+  </si>
+  <si>
+    <t>0.8745,0.0129,0.1321,0.0005</t>
+  </si>
+  <si>
+    <t>0.9098,0.0065,0.0900,0.0005</t>
+  </si>
+  <si>
+    <t>0.7765,0.2410,0.0487,0.0014</t>
+  </si>
+  <si>
+    <t>0.7297,0.1788,0.1230,0.0035</t>
+  </si>
+  <si>
+    <t>0.0750,0.0475,0.9573,0.0034</t>
+  </si>
+  <si>
+    <t>0.8851,0.0498,0.0651,0.0007</t>
+  </si>
+  <si>
+    <t>0.6908,0.1440,0.0826,0.0147</t>
+  </si>
+  <si>
+    <t>0.6599,0.1210,0.2744,0.0096</t>
+  </si>
+  <si>
+    <t>0.7716,0.1451,0.0778,0.0055</t>
+  </si>
+  <si>
+    <t>0.8148,0.1248,0.0544,0.0051</t>
+  </si>
+  <si>
+    <t>0.6677,0.1657,0.1189,0.0027</t>
+  </si>
+  <si>
+    <t>0.8673,0.0040,0.1673,0.0004</t>
+  </si>
+  <si>
+    <t>0.8994,0.0055,0.1053,0.0007</t>
+  </si>
+  <si>
+    <t>0.9675,0.0018,0.0252,0.0002</t>
+  </si>
+  <si>
+    <t>0.9052,0.0031,0.1207,0.0003</t>
+  </si>
+  <si>
+    <t>0.9547,0.0101,0.0172,0.0002</t>
+  </si>
+  <si>
+    <t>0.8955,0.0158,0.1019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9163,0.0277,0.0370,0.0014</t>
+  </si>
+  <si>
+    <t>0.8766,0.1386,0.0194,0.0007</t>
+  </si>
+  <si>
+    <t>0.1916,0.8688,0.0725,0.0012</t>
+  </si>
+  <si>
+    <t>0.3607,0.7614,0.0673,0.0012</t>
+  </si>
+  <si>
+    <t>0.7799,0.0151,0.2306,0.0010</t>
+  </si>
+  <si>
+    <t>0.7407,0.0232,0.3057,0.0005</t>
+  </si>
+  <si>
+    <t>0.8391,0.0060,0.2450,0.0002</t>
+  </si>
+  <si>
+    <t>0.8056,0.0211,0.2355,0.0006</t>
+  </si>
+  <si>
+    <t>0.6364,0.0144,0.5573,0.0008</t>
+  </si>
+  <si>
+    <t>0.7784,0.0075,0.3861,0.0003</t>
+  </si>
+  <si>
+    <t>0.7787,0.1439,0.0580,0.0083</t>
+  </si>
+  <si>
+    <t>0.8236,0.0580,0.0235,0.0168</t>
+  </si>
+  <si>
+    <t>0.8113,0.0999,0.0549,0.0055</t>
+  </si>
+  <si>
+    <t>0.6964,0.0376,0.3614,0.0051</t>
+  </si>
+  <si>
+    <t>0.7299,0.1412,0.0762,0.0106</t>
+  </si>
+  <si>
+    <t>0.7756,0.0690,0.0548,0.0183</t>
+  </si>
+  <si>
+    <t>0.7904,0.1217,0.0597,0.0086</t>
+  </si>
+  <si>
+    <t>0.4729,0.0689,0.5135,0.0004</t>
+  </si>
+  <si>
+    <t>0.6974,0.0099,0.4755,0.0002</t>
+  </si>
+  <si>
+    <t>0.4977,0.0068,0.7285,0.0002</t>
+  </si>
+  <si>
+    <t>0.3583,0.2319,0.3621,0.0003</t>
+  </si>
+  <si>
+    <t>0.5641,0.0181,0.5713,0.0036</t>
+  </si>
+  <si>
+    <t>0.8419,0.1789,0.0252,0.0004</t>
+  </si>
+  <si>
+    <t>0.0189,0.9857,0.0237,0.0006</t>
+  </si>
+  <si>
+    <t>0.9110,0.0513,0.0197,0.0014</t>
+  </si>
+  <si>
+    <t>0.8989,0.0508,0.0250,0.0021</t>
+  </si>
+  <si>
+    <t>0.3591,0.4082,0.3753,0.0075</t>
+  </si>
+  <si>
+    <t>0.8066,0.0185,0.2126,0.0002</t>
+  </si>
+  <si>
+    <t>0.9199,0.0140,0.0506,0.0001</t>
+  </si>
+  <si>
+    <t>0.7197,0.1485,0.0711,0.0001</t>
+  </si>
+  <si>
+    <t>0.5216,0.4415,0.0762,0.0005</t>
+  </si>
+  <si>
+    <t>0.9132,0.0230,0.0373,0.0015</t>
+  </si>
+  <si>
+    <t>0.8005,0.0530,0.0748,0.0162</t>
+  </si>
+  <si>
+    <t>0.8480,0.0435,0.0133,0.0128</t>
+  </si>
+  <si>
+    <t>0.9123,0.0217,0.0282,0.0030</t>
+  </si>
+  <si>
+    <t>0.8636,0.0332,0.0784,0.0057</t>
+  </si>
+  <si>
+    <t>0.8418,0.0576,0.0244,0.0146</t>
+  </si>
+  <si>
+    <t>0.7047,0.2321,0.0481,0.0003</t>
+  </si>
+  <si>
+    <t>0.6097,0.0206,0.4777,0.0006</t>
+  </si>
+  <si>
+    <t>0.8746,0.0836,0.0316,0.0003</t>
+  </si>
+  <si>
+    <t>0.4604,0.4029,0.1234,0.0025</t>
+  </si>
+  <si>
+    <t>0.4489,0.2137,0.2630,0.0003</t>
+  </si>
+  <si>
+    <t>0.8984,0.0461,0.0297,0.0002</t>
+  </si>
+  <si>
+    <t>0.8188,0.0583,0.0519,0.0153</t>
+  </si>
+  <si>
+    <t>0.7637,0.0817,0.0504,0.0235</t>
+  </si>
+  <si>
+    <t>0.8512,0.0650,0.0322,0.0044</t>
+  </si>
+  <si>
+    <t>0.8544,0.0692,0.0271,0.0048</t>
+  </si>
+  <si>
+    <t>0.7574,0.1466,0.0662,0.0048</t>
+  </si>
+  <si>
+    <t>0.7530,0.1138,0.0618,0.0131</t>
+  </si>
+  <si>
+    <t>0.7179,0.1515,0.0940,0.0112</t>
+  </si>
+  <si>
+    <t>0.7177,0.0996,0.0561,0.0234</t>
+  </si>
+  <si>
+    <t>0.7838,0.0398,0.0287,0.0394</t>
+  </si>
+  <si>
+    <t>0.8124,0.0532,0.0401,0.0157</t>
+  </si>
+  <si>
+    <t>0.7165,0.1392,0.0652,0.0124</t>
+  </si>
+  <si>
+    <t>0.7696,0.0636,0.0855,0.0120</t>
+  </si>
+  <si>
+    <t>0.7354,0.1341,0.0633,0.0123</t>
+  </si>
+  <si>
+    <t>0.8341,0.0358,0.0188,0.0151</t>
+  </si>
+  <si>
+    <t>0.7292,0.1400,0.0441,0.0120</t>
+  </si>
+  <si>
+    <t>0.8231,0.0560,0.0210,0.0160</t>
+  </si>
+  <si>
+    <t>0.2931,0.0189,0.8281,0.0017</t>
+  </si>
+  <si>
+    <t>0.8501,0.0162,0.1787,0.0007</t>
+  </si>
+  <si>
+    <t>0.9632,0.0071,0.0206,0.0002</t>
+  </si>
+  <si>
+    <t>0.8634,0.0161,0.1128,0.0027</t>
+  </si>
+  <si>
+    <t>0.7026,0.2820,0.0572,0.0035</t>
+  </si>
+  <si>
+    <t>0.4978,0.5512,0.0689,0.0034</t>
+  </si>
+  <si>
+    <t>0.3695,0.6697,0.1096,0.0055</t>
+  </si>
+  <si>
+    <t>0.3947,0.6553,0.0650,0.0056</t>
+  </si>
+  <si>
+    <t>0.6022,0.4398,0.0410,0.0045</t>
+  </si>
+  <si>
+    <t>0.4197,0.6445,0.0667,0.0022</t>
+  </si>
+  <si>
+    <t>0.8113,0.0971,0.0666,0.0036</t>
+  </si>
+  <si>
+    <t>0.8843,0.0582,0.0211,0.0024</t>
+  </si>
+  <si>
+    <t>0.8545,0.0273,0.1226,0.0027</t>
+  </si>
+  <si>
+    <t>0.8845,0.0338,0.0643,0.0041</t>
+  </si>
+  <si>
+    <t>0.9200,0.0426,0.0230,0.0009</t>
+  </si>
+  <si>
+    <t>0.8178,0.0676,0.0776,0.0097</t>
+  </si>
+  <si>
+    <t>0.5967,0.5434,0.0346,0.0004</t>
+  </si>
+  <si>
+    <t>0.3462,0.7557,0.0592,0.0006</t>
+  </si>
+  <si>
+    <t>0.8564,0.1245,0.0490,0.0006</t>
+  </si>
+  <si>
+    <t>0.2487,0.7407,0.1665,0.0022</t>
+  </si>
+  <si>
+    <t>0.8113,0.1542,0.0416,0.0011</t>
+  </si>
+  <si>
+    <t>0.7245,0.1370,0.1396,0.0040</t>
+  </si>
+  <si>
+    <t>0.9321,0.0342,0.0265,0.0006</t>
+  </si>
+  <si>
+    <t>0.8770,0.0524,0.0410,0.0029</t>
+  </si>
+  <si>
+    <t>0.6920,0.1173,0.0596,0.0230</t>
+  </si>
+  <si>
+    <t>0.7537,0.0636,0.0471,0.0273</t>
+  </si>
+  <si>
+    <t>0.7859,0.1086,0.1059,0.0053</t>
+  </si>
+  <si>
+    <t>0.9042,0.0192,0.0334,0.0056</t>
+  </si>
+  <si>
+    <t>0.7094,0.1306,0.0761,0.0138</t>
+  </si>
+  <si>
+    <t>0.8029,0.1019,0.0379,0.0075</t>
+  </si>
+  <si>
+    <t>0.8622,0.0587,0.0477,0.0028</t>
+  </si>
+  <si>
+    <t>0.7272,0.0215,0.2975,0.0003</t>
+  </si>
+  <si>
+    <t>0.5659,0.1559,0.1738,0.0004</t>
+  </si>
+  <si>
+    <t>0.6686,0.0332,0.3332,0.0005</t>
+  </si>
+  <si>
+    <t>0.9250,0.0035,0.0668,0.0003</t>
+  </si>
+  <si>
+    <t>0.9607,0.0081,0.0217,0.0002</t>
+  </si>
+  <si>
+    <t>0.8213,0.1308,0.0456,0.0015</t>
+  </si>
+  <si>
+    <t>0.8809,0.0468,0.1024,0.0006</t>
+  </si>
+  <si>
+    <t>0.8999,0.0383,0.0376,0.0012</t>
+  </si>
+  <si>
+    <t>0.9360,0.0226,0.0143,0.0032</t>
+  </si>
+  <si>
+    <t>0.7971,0.0321,0.0287,0.0263</t>
+  </si>
+  <si>
+    <t>0.9547,0.0112,0.0092,0.0017</t>
+  </si>
+  <si>
+    <t>0.9091,0.0078,0.0324,0.0039</t>
+  </si>
+  <si>
+    <t>0.3862,0.4516,0.2002,0.0033</t>
+  </si>
+  <si>
+    <t>0.8593,0.0652,0.0509,0.0027</t>
+  </si>
+  <si>
+    <t>0.7641,0.1383,0.0540,0.0087</t>
+  </si>
+  <si>
+    <t>0.7154,0.0543,0.0669,0.0586</t>
+  </si>
+  <si>
+    <t>0.7463,0.1874,0.0954,0.0060</t>
+  </si>
+  <si>
+    <t>0.9119,0.0323,0.0315,0.0019</t>
+  </si>
+  <si>
+    <t>0.8970,0.0417,0.0259,0.0031</t>
+  </si>
+  <si>
+    <t>0.6212,0.1756,0.1304,0.0275</t>
+  </si>
+  <si>
+    <t>0.0587,0.4093,0.8760,0.0167</t>
+  </si>
+  <si>
+    <t>0.8971,0.0516,0.0255,0.0028</t>
+  </si>
+  <si>
+    <t>0.6815,0.1377,0.0377,0.0274</t>
+  </si>
+  <si>
+    <t>0.6927,0.2657,0.0681,0.0050</t>
+  </si>
+  <si>
+    <t>0.8694,0.0507,0.0407,0.0046</t>
+  </si>
+  <si>
+    <t>0.8826,0.0522,0.0535,0.0013</t>
+  </si>
+  <si>
+    <t>0.6598,0.2166,0.1401,0.0057</t>
+  </si>
+  <si>
+    <t>0.5257,0.4848,0.0974,0.0074</t>
+  </si>
+  <si>
+    <t>0.8733,0.0578,0.0541,0.0020</t>
+  </si>
+  <si>
+    <t>0.6538,0.2231,0.0821,0.0157</t>
+  </si>
+  <si>
+    <t>0.7652,0.0809,0.0547,0.0207</t>
+  </si>
+  <si>
+    <t>0.6980,0.1013,0.0435,0.0294</t>
+  </si>
+  <si>
+    <t>0.8856,0.0410,0.0213,0.0075</t>
+  </si>
+  <si>
+    <t>0.7313,0.0992,0.0269,0.0194</t>
+  </si>
+  <si>
+    <t>0.7488,0.0788,0.0669,0.0206</t>
+  </si>
+  <si>
+    <t>0.7439,0.0657,0.0539,0.0252</t>
+  </si>
+  <si>
+    <t>0.7361,0.1204,0.0922,0.0164</t>
+  </si>
+  <si>
+    <t>0.6613,0.2103,0.0480,0.0090</t>
+  </si>
+  <si>
+    <t>0.7508,0.1114,0.0663,0.0136</t>
+  </si>
+  <si>
+    <t>0.7840,0.1577,0.0369,0.0055</t>
+  </si>
+  <si>
+    <t>0.7181,0.1233,0.0409,0.0141</t>
+  </si>
+  <si>
+    <t>0.6600,0.1878,0.0582,0.0115</t>
+  </si>
+  <si>
+    <t>0.7690,0.1516,0.0600,0.0055</t>
+  </si>
+  <si>
+    <t>0.7417,0.0849,0.0657,0.0226</t>
+  </si>
+  <si>
+    <t>0.8105,0.1056,0.0641,0.0045</t>
+  </si>
+  <si>
+    <t>0.4529,0.1784,0.5011,0.0037</t>
+  </si>
+  <si>
+    <t>0.6749,0.1279,0.1231,0.0344</t>
+  </si>
+  <si>
+    <t>0.8567,0.0059,0.2008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9267,0.0200,0.0403,0.0004</t>
+  </si>
+  <si>
+    <t>0.7422,0.0261,0.3086,0.0022</t>
+  </si>
+  <si>
+    <t>0.3519,0.0623,0.6535,0.0015</t>
+  </si>
+  <si>
+    <t>0.9261,0.0055,0.0931,0.0004</t>
+  </si>
+  <si>
+    <t>0.9436,0.0067,0.0466,0.0001</t>
+  </si>
+  <si>
+    <t>0.8713,0.0040,0.1949,0.0003</t>
+  </si>
+  <si>
+    <t>0.9124,0.0315,0.0347,0.0011</t>
+  </si>
+  <si>
+    <t>0.9048,0.0369,0.0440,0.0011</t>
+  </si>
+  <si>
+    <t>0.8356,0.0780,0.0620,0.0033</t>
+  </si>
+  <si>
+    <t>0.8301,0.0498,0.1261,0.0007</t>
+  </si>
+  <si>
+    <t>0.8559,0.0851,0.0632,0.0011</t>
+  </si>
+  <si>
+    <t>0.7601,0.1573,0.1040,0.0012</t>
+  </si>
+  <si>
+    <t>0.9149,0.0292,0.0320,0.0008</t>
+  </si>
+  <si>
+    <t>0.8156,0.0691,0.0911,0.0054</t>
+  </si>
+  <si>
+    <t>0.8137,0.0922,0.0368,0.0118</t>
+  </si>
+  <si>
+    <t>0.8031,0.1372,0.0536,0.0042</t>
+  </si>
+  <si>
+    <t>0.7589,0.1008,0.0706,0.0117</t>
+  </si>
+  <si>
+    <t>0.5857,0.2507,0.0874,0.0181</t>
+  </si>
+  <si>
+    <t>0.7780,0.0899,0.0672,0.0080</t>
+  </si>
+  <si>
+    <t>0.6572,0.3933,0.0705,0.0013</t>
+  </si>
+  <si>
+    <t>0.8675,0.0307,0.0975,0.0020</t>
+  </si>
+  <si>
+    <t>0.8933,0.0216,0.1110,0.0008</t>
+  </si>
+  <si>
+    <t>0.9163,0.0304,0.0464,0.0003</t>
+  </si>
+  <si>
+    <t>0.9247,0.0236,0.0339,0.0009</t>
+  </si>
+  <si>
+    <t>0.7188,0.0372,0.3115,0.0013</t>
+  </si>
+  <si>
+    <t>0.7572,0.0282,0.2931,0.0015</t>
+  </si>
+  <si>
+    <t>0.9364,0.0082,0.0456,0.0003</t>
+  </si>
+  <si>
+    <t>0.7768,0.0184,0.2339,0.0027</t>
+  </si>
+  <si>
+    <t>0.7704,0.0622,0.1504,0.0009</t>
+  </si>
+  <si>
+    <t>0.9018,0.0368,0.0248,0.0043</t>
+  </si>
+  <si>
+    <t>0.7278,0.1326,0.0476,0.0125</t>
+  </si>
+  <si>
+    <t>0.7658,0.1360,0.0611,0.0074</t>
+  </si>
+  <si>
+    <t>0.7452,0.1076,0.0318,0.0151</t>
+  </si>
+  <si>
+    <t>0.7222,0.1350,0.0658,0.0162</t>
+  </si>
+  <si>
+    <t>0.7651,0.0790,0.0299,0.0184</t>
+  </si>
+  <si>
+    <t>0.7392,0.1622,0.0531,0.0121</t>
+  </si>
+  <si>
+    <t>0.8117,0.1038,0.0484,0.0052</t>
+  </si>
+  <si>
+    <t>0.8480,0.0797,0.0679,0.0031</t>
+  </si>
+  <si>
+    <t>0.8350,0.1189,0.0492,0.0032</t>
+  </si>
+  <si>
+    <t>0.8057,0.1205,0.0690,0.0030</t>
+  </si>
+  <si>
+    <t>0.8945,0.0062,0.1202,0.0002</t>
+  </si>
+  <si>
+    <t>0.5763,0.0217,0.5205,0.0012</t>
+  </si>
+  <si>
+    <t>0.7547,0.0232,0.3058,0.0004</t>
+  </si>
+  <si>
+    <t>0.3995,0.0107,0.8117,0.0003</t>
+  </si>
+  <si>
+    <t>0.8549,0.0172,0.1817,0.0005</t>
+  </si>
+  <si>
+    <t>0.7130,0.0098,0.4374,0.0006</t>
+  </si>
+  <si>
+    <t>0.9664,0.0019,0.0297,0.0001</t>
+  </si>
+  <si>
+    <t>0.7972,0.0378,0.2262,0.0051</t>
+  </si>
+  <si>
+    <t>0.9249,0.0146,0.0569,0.0006</t>
+  </si>
+  <si>
+    <t>0.8910,0.0364,0.0637,0.0006</t>
+  </si>
+  <si>
+    <t>0.9348,0.0239,0.0205,0.0012</t>
+  </si>
+  <si>
+    <t>0.8443,0.0508,0.0401,0.0101</t>
+  </si>
+  <si>
+    <t>0.5527,0.3426,0.0792,0.0159</t>
+  </si>
+  <si>
+    <t>0.8034,0.0803,0.0340,0.0172</t>
+  </si>
+  <si>
+    <t>0.7868,0.0738,0.0553,0.0140</t>
+  </si>
+  <si>
+    <t>0.8648,0.0288,0.0314,0.0137</t>
+  </si>
+  <si>
+    <t>0.8697,0.0766,0.0365,0.0035</t>
+  </si>
+  <si>
+    <t>0.8072,0.0757,0.0437,0.0082</t>
+  </si>
+  <si>
+    <t>0.6611,0.0916,0.0428,0.0324</t>
+  </si>
+  <si>
+    <t>0.7096,0.2240,0.0730,0.0007</t>
+  </si>
+  <si>
+    <t>0.5125,0.1082,0.3751,0.0009</t>
+  </si>
+  <si>
+    <t>0.9149,0.0078,0.0725,0.0003</t>
+  </si>
+  <si>
+    <t>0.8553,0.0845,0.0439,0.0013</t>
+  </si>
+  <si>
+    <t>0.8625,0.0065,0.2177,0.0003</t>
+  </si>
+  <si>
+    <t>0.9099,0.0212,0.0480,0.0011</t>
+  </si>
+  <si>
+    <t>0.8602,0.0249,0.1350,0.0008</t>
+  </si>
+  <si>
+    <t>0.9066,0.0061,0.0842,0.0014</t>
+  </si>
+  <si>
+    <t>0.8457,0.0756,0.0487,0.0041</t>
+  </si>
+  <si>
+    <t>0.9421,0.0179,0.0193,0.0008</t>
+  </si>
+  <si>
+    <t>0.9141,0.0390,0.0211,0.0029</t>
+  </si>
+  <si>
+    <t>0.8108,0.0677,0.0505,0.0138</t>
+  </si>
+  <si>
+    <t>0.8725,0.0202,0.0418,0.0127</t>
+  </si>
+  <si>
+    <t>0.8338,0.0713,0.0790,0.0031</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7773,0.1153,0.0752,0.0081</t>
-  </si>
-  <si>
-    <t>0.8124,0.0693,0.0430,0.0104</t>
-  </si>
-  <si>
-    <t>0.8561,0.0501,0.0393,0.0068</t>
-  </si>
-  <si>
-    <t>0.7005,0.2455,0.0468,0.0074</t>
-  </si>
-  <si>
-    <t>0.8500,0.0725,0.0451,0.0058</t>
-  </si>
-  <si>
-    <t>0.8517,0.0625,0.0471,0.0061</t>
-  </si>
-  <si>
-    <t>0.7412,0.1142,0.0476,0.0181</t>
-  </si>
-  <si>
-    <t>0.7524,0.0860,0.0450,0.0221</t>
-  </si>
-  <si>
-    <t>0.7215,0.1646,0.0516,0.0105</t>
-  </si>
-  <si>
-    <t>0.7361,0.1182,0.0468,0.0158</t>
-  </si>
-  <si>
-    <t>0.8113,0.0499,0.0255,0.0187</t>
-  </si>
-  <si>
-    <t>0.5885,0.2198,0.0430,0.0176</t>
-  </si>
-  <si>
-    <t>0.8643,0.0555,0.0818,0.0004</t>
-  </si>
-  <si>
-    <t>0.9047,0.0205,0.0775,0.0011</t>
-  </si>
-  <si>
-    <t>0.9082,0.0239,0.0607,0.0009</t>
-  </si>
-  <si>
-    <t>0.6964,0.1562,0.1594,0.0023</t>
-  </si>
-  <si>
-    <t>0.8917,0.0465,0.0431,0.0014</t>
-  </si>
-  <si>
-    <t>0.4785,0.5890,0.0868,0.0016</t>
-  </si>
-  <si>
-    <t>0.7783,0.1506,0.0608,0.0033</t>
-  </si>
-  <si>
-    <t>0.7868,0.1186,0.0859,0.0052</t>
-  </si>
-  <si>
-    <t>0.1813,0.8469,0.1308,0.0075</t>
-  </si>
-  <si>
-    <t>0.2757,0.7844,0.0883,0.0027</t>
-  </si>
-  <si>
-    <t>0.9005,0.0169,0.1119,0.0003</t>
-  </si>
-  <si>
-    <t>0.9352,0.0152,0.0464,0.0003</t>
-  </si>
-  <si>
-    <t>0.8914,0.0222,0.0635,0.0002</t>
-  </si>
-  <si>
-    <t>0.9091,0.0118,0.0741,0.0010</t>
-  </si>
-  <si>
-    <t>0.8435,0.0117,0.2138,0.0006</t>
-  </si>
-  <si>
-    <t>0.8745,0.0129,0.1321,0.0005</t>
-  </si>
-  <si>
-    <t>0.9098,0.0065,0.0900,0.0005</t>
-  </si>
-  <si>
-    <t>0.7765,0.2410,0.0487,0.0014</t>
-  </si>
-  <si>
-    <t>0.7297,0.1788,0.1230,0.0035</t>
-  </si>
-  <si>
-    <t>0.0750,0.0475,0.9573,0.0034</t>
-  </si>
-  <si>
-    <t>0.8851,0.0498,0.0651,0.0007</t>
-  </si>
-  <si>
-    <t>0.6908,0.1440,0.0826,0.0147</t>
-  </si>
-  <si>
-    <t>0.6599,0.1210,0.2744,0.0096</t>
-  </si>
-  <si>
-    <t>0.7716,0.1451,0.0778,0.0055</t>
-  </si>
-  <si>
-    <t>0.8148,0.1248,0.0544,0.0051</t>
-  </si>
-  <si>
-    <t>0.6677,0.1657,0.1189,0.0027</t>
-  </si>
-  <si>
-    <t>0.8673,0.0040,0.1673,0.0004</t>
-  </si>
-  <si>
-    <t>0.8994,0.0055,0.1053,0.0007</t>
-  </si>
-  <si>
-    <t>0.9675,0.0018,0.0252,0.0002</t>
-  </si>
-  <si>
-    <t>0.9052,0.0031,0.1207,0.0003</t>
-  </si>
-  <si>
-    <t>0.9547,0.0101,0.0172,0.0002</t>
-  </si>
-  <si>
-    <t>0.8955,0.0158,0.1019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9163,0.0277,0.0370,0.0014</t>
-  </si>
-  <si>
-    <t>0.8766,0.1386,0.0194,0.0007</t>
-  </si>
-  <si>
-    <t>0.1916,0.8688,0.0725,0.0012</t>
-  </si>
-  <si>
-    <t>0.3607,0.7614,0.0673,0.0012</t>
-  </si>
-  <si>
-    <t>0.7799,0.0151,0.2306,0.0010</t>
-  </si>
-  <si>
-    <t>0.7407,0.0232,0.3057,0.0005</t>
-  </si>
-  <si>
-    <t>0.8391,0.0060,0.2450,0.0002</t>
-  </si>
-  <si>
-    <t>0.8056,0.0211,0.2355,0.0006</t>
-  </si>
-  <si>
-    <t>0.6364,0.0144,0.5573,0.0008</t>
-  </si>
-  <si>
-    <t>0.7784,0.0075,0.3861,0.0003</t>
-  </si>
-  <si>
-    <t>0.7787,0.1439,0.0580,0.0083</t>
-  </si>
-  <si>
-    <t>0.8236,0.0580,0.0235,0.0168</t>
-  </si>
-  <si>
-    <t>0.8113,0.0999,0.0549,0.0055</t>
-  </si>
-  <si>
-    <t>0.6964,0.0376,0.3614,0.0051</t>
-  </si>
-  <si>
-    <t>0.7299,0.1412,0.0762,0.0106</t>
-  </si>
-  <si>
-    <t>0.7756,0.0690,0.0548,0.0183</t>
-  </si>
-  <si>
-    <t>0.7904,0.1217,0.0597,0.0086</t>
-  </si>
-  <si>
-    <t>0.4729,0.0689,0.5135,0.0004</t>
-  </si>
-  <si>
-    <t>0.6974,0.0099,0.4755,0.0002</t>
-  </si>
-  <si>
-    <t>0.4977,0.0068,0.7285,0.0002</t>
-  </si>
-  <si>
-    <t>0.3583,0.2319,0.3621,0.0003</t>
-  </si>
-  <si>
-    <t>0.5641,0.0181,0.5713,0.0036</t>
-  </si>
-  <si>
-    <t>0.8419,0.1789,0.0252,0.0004</t>
-  </si>
-  <si>
-    <t>0.0189,0.9857,0.0237,0.0006</t>
-  </si>
-  <si>
-    <t>0.9110,0.0513,0.0197,0.0014</t>
-  </si>
-  <si>
-    <t>0.8989,0.0508,0.0250,0.0021</t>
-  </si>
-  <si>
-    <t>0.3591,0.4082,0.3753,0.0075</t>
-  </si>
-  <si>
-    <t>0.8066,0.0185,0.2126,0.0002</t>
-  </si>
-  <si>
-    <t>0.9199,0.0140,0.0506,0.0001</t>
-  </si>
-  <si>
-    <t>0.7197,0.1485,0.0711,0.0001</t>
-  </si>
-  <si>
-    <t>0.5216,0.4415,0.0762,0.0005</t>
-  </si>
-  <si>
-    <t>0.9132,0.0230,0.0373,0.0015</t>
-  </si>
-  <si>
-    <t>0.8005,0.0530,0.0748,0.0162</t>
-  </si>
-  <si>
-    <t>0.8480,0.0435,0.0133,0.0128</t>
-  </si>
-  <si>
-    <t>0.9123,0.0217,0.0282,0.0030</t>
-  </si>
-  <si>
-    <t>0.8636,0.0332,0.0784,0.0057</t>
-  </si>
-  <si>
-    <t>0.8418,0.0576,0.0244,0.0146</t>
-  </si>
-  <si>
-    <t>0.7047,0.2321,0.0481,0.0003</t>
-  </si>
-  <si>
-    <t>0.6097,0.0206,0.4777,0.0006</t>
-  </si>
-  <si>
-    <t>0.8746,0.0836,0.0316,0.0003</t>
-  </si>
-  <si>
-    <t>0.4604,0.4029,0.1234,0.0025</t>
-  </si>
-  <si>
-    <t>0.4489,0.2137,0.2630,0.0003</t>
-  </si>
-  <si>
-    <t>0.8984,0.0461,0.0297,0.0002</t>
-  </si>
-  <si>
-    <t>0.8188,0.0583,0.0519,0.0153</t>
-  </si>
-  <si>
-    <t>0.7637,0.0817,0.0504,0.0235</t>
-  </si>
-  <si>
-    <t>0.8512,0.0650,0.0322,0.0044</t>
-  </si>
-  <si>
-    <t>0.8544,0.0692,0.0271,0.0048</t>
-  </si>
-  <si>
-    <t>0.7574,0.1466,0.0662,0.0048</t>
-  </si>
-  <si>
-    <t>0.7530,0.1138,0.0618,0.0131</t>
-  </si>
-  <si>
-    <t>0.7179,0.1515,0.0940,0.0112</t>
-  </si>
-  <si>
-    <t>0.7177,0.0996,0.0561,0.0234</t>
-  </si>
-  <si>
-    <t>0.7838,0.0398,0.0287,0.0394</t>
-  </si>
-  <si>
-    <t>0.8124,0.0532,0.0401,0.0157</t>
-  </si>
-  <si>
-    <t>0.7165,0.1392,0.0652,0.0124</t>
-  </si>
-  <si>
-    <t>0.7696,0.0636,0.0855,0.0120</t>
-  </si>
-  <si>
-    <t>0.7354,0.1341,0.0633,0.0123</t>
-  </si>
-  <si>
-    <t>0.8341,0.0358,0.0188,0.0151</t>
-  </si>
-  <si>
-    <t>0.7292,0.1400,0.0441,0.0120</t>
-  </si>
-  <si>
-    <t>0.8231,0.0560,0.0210,0.0160</t>
-  </si>
-  <si>
-    <t>0.2931,0.0189,0.8281,0.0017</t>
-  </si>
-  <si>
-    <t>0.8501,0.0162,0.1787,0.0007</t>
-  </si>
-  <si>
-    <t>0.9632,0.0071,0.0206,0.0002</t>
-  </si>
-  <si>
-    <t>0.8634,0.0161,0.1128,0.0027</t>
-  </si>
-  <si>
-    <t>0.7026,0.2820,0.0572,0.0035</t>
-  </si>
-  <si>
-    <t>0.4978,0.5512,0.0689,0.0034</t>
-  </si>
-  <si>
-    <t>0.3695,0.6697,0.1096,0.0055</t>
-  </si>
-  <si>
-    <t>0.3947,0.6553,0.0650,0.0056</t>
-  </si>
-  <si>
-    <t>0.6022,0.4398,0.0410,0.0045</t>
-  </si>
-  <si>
-    <t>0.4197,0.6445,0.0667,0.0022</t>
-  </si>
-  <si>
-    <t>0.8113,0.0971,0.0666,0.0036</t>
-  </si>
-  <si>
-    <t>0.8843,0.0582,0.0211,0.0024</t>
-  </si>
-  <si>
-    <t>0.8545,0.0273,0.1226,0.0027</t>
-  </si>
-  <si>
-    <t>0.8845,0.0338,0.0643,0.0041</t>
-  </si>
-  <si>
-    <t>0.9200,0.0426,0.0230,0.0009</t>
-  </si>
-  <si>
-    <t>0.8178,0.0676,0.0776,0.0097</t>
-  </si>
-  <si>
-    <t>0.5967,0.5434,0.0346,0.0004</t>
-  </si>
-  <si>
-    <t>0.3462,0.7557,0.0592,0.0006</t>
-  </si>
-  <si>
-    <t>0.8564,0.1245,0.0490,0.0006</t>
-  </si>
-  <si>
-    <t>0.2487,0.7407,0.1665,0.0022</t>
-  </si>
-  <si>
-    <t>0.8113,0.1542,0.0416,0.0011</t>
-  </si>
-  <si>
-    <t>0.7245,0.1370,0.1396,0.0040</t>
-  </si>
-  <si>
-    <t>0.9321,0.0342,0.0265,0.0006</t>
-  </si>
-  <si>
-    <t>0.8770,0.0524,0.0410,0.0029</t>
-  </si>
-  <si>
-    <t>0.6920,0.1173,0.0596,0.0230</t>
-  </si>
-  <si>
-    <t>0.7537,0.0636,0.0471,0.0273</t>
-  </si>
-  <si>
-    <t>0.7859,0.1086,0.1059,0.0053</t>
-  </si>
-  <si>
-    <t>0.9042,0.0192,0.0334,0.0056</t>
-  </si>
-  <si>
-    <t>0.7094,0.1306,0.0761,0.0138</t>
-  </si>
-  <si>
-    <t>0.8029,0.1019,0.0379,0.0075</t>
-  </si>
-  <si>
-    <t>0.8622,0.0587,0.0477,0.0028</t>
-  </si>
-  <si>
-    <t>0.7272,0.0215,0.2975,0.0003</t>
-  </si>
-  <si>
-    <t>0.5659,0.1559,0.1738,0.0004</t>
-  </si>
-  <si>
-    <t>0.6686,0.0332,0.3332,0.0005</t>
-  </si>
-  <si>
-    <t>0.9250,0.0035,0.0668,0.0003</t>
-  </si>
-  <si>
-    <t>0.9607,0.0081,0.0217,0.0002</t>
-  </si>
-  <si>
-    <t>0.8213,0.1308,0.0456,0.0015</t>
-  </si>
-  <si>
-    <t>0.8809,0.0468,0.1024,0.0006</t>
-  </si>
-  <si>
-    <t>0.8999,0.0383,0.0376,0.0012</t>
-  </si>
-  <si>
-    <t>0.9360,0.0226,0.0143,0.0032</t>
-  </si>
-  <si>
-    <t>0.7971,0.0321,0.0287,0.0263</t>
-  </si>
-  <si>
-    <t>0.9547,0.0112,0.0092,0.0017</t>
-  </si>
-  <si>
-    <t>0.9091,0.0078,0.0324,0.0039</t>
-  </si>
-  <si>
-    <t>0.3862,0.4516,0.2002,0.0033</t>
-  </si>
-  <si>
-    <t>0.8593,0.0652,0.0509,0.0027</t>
-  </si>
-  <si>
-    <t>0.7641,0.1383,0.0540,0.0087</t>
-  </si>
-  <si>
-    <t>0.7154,0.0543,0.0669,0.0586</t>
-  </si>
-  <si>
-    <t>0.7463,0.1874,0.0954,0.0060</t>
-  </si>
-  <si>
-    <t>0.9119,0.0323,0.0315,0.0019</t>
-  </si>
-  <si>
-    <t>0.8970,0.0417,0.0259,0.0031</t>
-  </si>
-  <si>
-    <t>0.6212,0.1756,0.1304,0.0275</t>
-  </si>
-  <si>
-    <t>0.0587,0.4093,0.8760,0.0167</t>
-  </si>
-  <si>
-    <t>0.8971,0.0516,0.0255,0.0028</t>
-  </si>
-  <si>
-    <t>0.6815,0.1377,0.0377,0.0274</t>
-  </si>
-  <si>
-    <t>0.6927,0.2657,0.0681,0.0050</t>
-  </si>
-  <si>
-    <t>0.8694,0.0507,0.0407,0.0046</t>
-  </si>
-  <si>
-    <t>0.8826,0.0522,0.0535,0.0013</t>
-  </si>
-  <si>
-    <t>0.6598,0.2166,0.1401,0.0057</t>
-  </si>
-  <si>
-    <t>0.5257,0.4848,0.0974,0.0074</t>
-  </si>
-  <si>
-    <t>0.8733,0.0578,0.0541,0.0020</t>
-  </si>
-  <si>
-    <t>0.6538,0.2231,0.0821,0.0157</t>
-  </si>
-  <si>
-    <t>0.7652,0.0809,0.0547,0.0207</t>
-  </si>
-  <si>
-    <t>0.6980,0.1013,0.0435,0.0294</t>
-  </si>
-  <si>
-    <t>0.8856,0.0410,0.0213,0.0075</t>
-  </si>
-  <si>
-    <t>0.7313,0.0992,0.0269,0.0194</t>
-  </si>
-  <si>
-    <t>0.7488,0.0788,0.0669,0.0206</t>
-  </si>
-  <si>
-    <t>0.7439,0.0657,0.0539,0.0252</t>
-  </si>
-  <si>
-    <t>0.7361,0.1204,0.0922,0.0164</t>
-  </si>
-  <si>
-    <t>0.6613,0.2103,0.0480,0.0090</t>
-  </si>
-  <si>
-    <t>0.7508,0.1114,0.0663,0.0136</t>
-  </si>
-  <si>
-    <t>0.7840,0.1577,0.0369,0.0055</t>
-  </si>
-  <si>
-    <t>0.7181,0.1233,0.0409,0.0141</t>
-  </si>
-  <si>
-    <t>0.6600,0.1878,0.0582,0.0115</t>
-  </si>
-  <si>
-    <t>0.7690,0.1516,0.0600,0.0055</t>
-  </si>
-  <si>
-    <t>0.7417,0.0849,0.0657,0.0226</t>
-  </si>
-  <si>
-    <t>0.8105,0.1056,0.0641,0.0045</t>
-  </si>
-  <si>
-    <t>0.4529,0.1784,0.5011,0.0037</t>
-  </si>
-  <si>
-    <t>0.6749,0.1279,0.1231,0.0344</t>
-  </si>
-  <si>
-    <t>0.8567,0.0059,0.2008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9267,0.0200,0.0403,0.0004</t>
-  </si>
-  <si>
-    <t>0.7422,0.0261,0.3086,0.0022</t>
-  </si>
-  <si>
-    <t>0.3519,0.0623,0.6535,0.0015</t>
-  </si>
-  <si>
-    <t>0.9261,0.0055,0.0931,0.0004</t>
-  </si>
-  <si>
-    <t>0.9436,0.0067,0.0466,0.0001</t>
-  </si>
-  <si>
-    <t>0.8713,0.0040,0.1949,0.0003</t>
-  </si>
-  <si>
-    <t>0.9124,0.0315,0.0347,0.0011</t>
-  </si>
-  <si>
-    <t>0.9048,0.0369,0.0440,0.0011</t>
-  </si>
-  <si>
-    <t>0.8356,0.0780,0.0620,0.0033</t>
-  </si>
-  <si>
-    <t>0.8301,0.0498,0.1261,0.0007</t>
-  </si>
-  <si>
-    <t>0.8559,0.0851,0.0632,0.0011</t>
-  </si>
-  <si>
-    <t>0.7601,0.1573,0.1040,0.0012</t>
-  </si>
-  <si>
-    <t>0.9149,0.0292,0.0320,0.0008</t>
-  </si>
-  <si>
-    <t>0.8156,0.0691,0.0911,0.0054</t>
-  </si>
-  <si>
-    <t>0.8137,0.0922,0.0368,0.0118</t>
-  </si>
-  <si>
-    <t>0.8031,0.1372,0.0536,0.0042</t>
-  </si>
-  <si>
-    <t>0.7589,0.1008,0.0706,0.0117</t>
-  </si>
-  <si>
-    <t>0.5857,0.2507,0.0874,0.0181</t>
-  </si>
-  <si>
-    <t>0.7780,0.0899,0.0672,0.0080</t>
-  </si>
-  <si>
-    <t>0.6572,0.3933,0.0705,0.0013</t>
-  </si>
-  <si>
-    <t>0.8675,0.0307,0.0975,0.0020</t>
-  </si>
-  <si>
-    <t>0.8933,0.0216,0.1110,0.0008</t>
-  </si>
-  <si>
-    <t>0.9163,0.0304,0.0464,0.0003</t>
-  </si>
-  <si>
-    <t>0.9247,0.0236,0.0339,0.0009</t>
-  </si>
-  <si>
-    <t>0.7188,0.0372,0.3115,0.0013</t>
-  </si>
-  <si>
-    <t>0.7572,0.0282,0.2931,0.0015</t>
-  </si>
-  <si>
-    <t>0.9364,0.0082,0.0456,0.0003</t>
-  </si>
-  <si>
-    <t>0.7768,0.0184,0.2339,0.0027</t>
-  </si>
-  <si>
-    <t>0.7704,0.0622,0.1504,0.0009</t>
-  </si>
-  <si>
-    <t>0.9018,0.0368,0.0248,0.0043</t>
-  </si>
-  <si>
-    <t>0.7278,0.1326,0.0476,0.0125</t>
-  </si>
-  <si>
-    <t>0.7658,0.1360,0.0611,0.0074</t>
-  </si>
-  <si>
-    <t>0.7452,0.1076,0.0318,0.0151</t>
-  </si>
-  <si>
-    <t>0.7222,0.1350,0.0658,0.0162</t>
-  </si>
-  <si>
-    <t>0.7651,0.0790,0.0299,0.0184</t>
-  </si>
-  <si>
-    <t>0.7392,0.1622,0.0531,0.0121</t>
-  </si>
-  <si>
-    <t>0.8117,0.1038,0.0484,0.0052</t>
-  </si>
-  <si>
-    <t>0.8480,0.0797,0.0679,0.0031</t>
-  </si>
-  <si>
-    <t>0.8350,0.1189,0.0492,0.0032</t>
-  </si>
-  <si>
-    <t>0.8057,0.1205,0.0690,0.0030</t>
-  </si>
-  <si>
-    <t>0.8945,0.0062,0.1202,0.0002</t>
-  </si>
-  <si>
-    <t>0.5763,0.0217,0.5205,0.0012</t>
-  </si>
-  <si>
-    <t>0.7547,0.0232,0.3058,0.0004</t>
-  </si>
-  <si>
-    <t>0.3995,0.0107,0.8117,0.0003</t>
-  </si>
-  <si>
-    <t>0.8549,0.0172,0.1817,0.0005</t>
-  </si>
-  <si>
-    <t>0.7130,0.0098,0.4374,0.0006</t>
-  </si>
-  <si>
-    <t>0.9664,0.0019,0.0297,0.0001</t>
-  </si>
-  <si>
-    <t>0.7972,0.0378,0.2262,0.0051</t>
-  </si>
-  <si>
-    <t>0.9249,0.0146,0.0569,0.0006</t>
-  </si>
-  <si>
-    <t>0.8910,0.0364,0.0637,0.0006</t>
-  </si>
-  <si>
-    <t>0.9348,0.0239,0.0205,0.0012</t>
-  </si>
-  <si>
-    <t>0.8443,0.0508,0.0401,0.0101</t>
-  </si>
-  <si>
-    <t>0.5527,0.3426,0.0792,0.0159</t>
-  </si>
-  <si>
-    <t>0.8034,0.0803,0.0340,0.0172</t>
-  </si>
-  <si>
-    <t>0.7868,0.0738,0.0553,0.0140</t>
-  </si>
-  <si>
-    <t>0.8648,0.0288,0.0314,0.0137</t>
-  </si>
-  <si>
-    <t>0.8697,0.0766,0.0365,0.0035</t>
-  </si>
-  <si>
-    <t>0.8072,0.0757,0.0437,0.0082</t>
-  </si>
-  <si>
-    <t>0.6611,0.0916,0.0428,0.0324</t>
-  </si>
-  <si>
-    <t>0.7096,0.2240,0.0730,0.0007</t>
-  </si>
-  <si>
-    <t>0.5125,0.1082,0.3751,0.0009</t>
-  </si>
-  <si>
-    <t>0.9149,0.0078,0.0725,0.0003</t>
-  </si>
-  <si>
-    <t>0.8553,0.0845,0.0439,0.0013</t>
-  </si>
-  <si>
-    <t>0.8625,0.0065,0.2177,0.0003</t>
-  </si>
-  <si>
-    <t>0.9099,0.0212,0.0480,0.0011</t>
-  </si>
-  <si>
-    <t>0.8602,0.0249,0.1350,0.0008</t>
-  </si>
-  <si>
-    <t>0.9066,0.0061,0.0842,0.0014</t>
-  </si>
-  <si>
-    <t>0.8457,0.0756,0.0487,0.0041</t>
-  </si>
-  <si>
-    <t>0.9421,0.0179,0.0193,0.0008</t>
-  </si>
-  <si>
-    <t>0.9141,0.0390,0.0211,0.0029</t>
-  </si>
-  <si>
-    <t>0.8108,0.0677,0.0505,0.0138</t>
-  </si>
-  <si>
-    <t>0.8725,0.0202,0.0418,0.0127</t>
-  </si>
-  <si>
-    <t>0.8338,0.0713,0.0790,0.0031</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9656,0.0083,0.0044,0.0132</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.9726,0.0010,0.0009,0.0174</t>
+  </si>
+  <si>
+    <t>0.0759,0.0013,0.0064,0.9631</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9940,0.0009,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9957,0.0012,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9920,0.0005,0.0003,0.0056</t>
+  </si>
+  <si>
+    <t>0.9896,0.0036,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9697,0.0195,0.0010,0.0054</t>
+  </si>
+  <si>
+    <t>0.9932,0.0006,0.0002,0.0034</t>
+  </si>
+  <si>
+    <t>0.9895,0.0044,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9531,0.0114,0.0247,0.0011</t>
+  </si>
+  <si>
+    <t>0.1569,0.0047,0.9261,0.0027</t>
+  </si>
+  <si>
+    <t>0.4134,0.0038,0.8242,0.0011</t>
+  </si>
+  <si>
+    <t>0.0855,0.0099,0.9506,0.0058</t>
+  </si>
+  <si>
+    <t>0.8434,0.0292,0.1079,0.0064</t>
+  </si>
+  <si>
+    <t>0.0011,0.9963,0.0011,0.0032</t>
+  </si>
+  <si>
+    <t>0.0016,0.9955,0.0021,0.0017</t>
+  </si>
+  <si>
+    <t>0.0182,0.9759,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.0004,0.9979,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.4282,0.0057,0.6279,0.0222</t>
+  </si>
+  <si>
+    <t>0.2461,0.0084,0.6189,0.0947</t>
+  </si>
+  <si>
+    <t>0.0027,0.0008,0.9970,0.0017</t>
+  </si>
+  <si>
+    <t>0.0174,0.0032,0.9858,0.0012</t>
+  </si>
+  <si>
+    <t>0.0607,0.0022,0.9744,0.0017</t>
+  </si>
+  <si>
+    <t>0.0118,0.0015,0.9698,0.0339</t>
+  </si>
+  <si>
+    <t>0.0022,0.0009,0.9937,0.0072</t>
+  </si>
+  <si>
+    <t>0.0406,0.9486,0.0086,0.0146</t>
+  </si>
+  <si>
+    <t>0.4459,0.0561,0.5916,0.0255</t>
+  </si>
+  <si>
+    <t>0.0016,0.0036,0.9949,0.0058</t>
+  </si>
+  <si>
+    <t>0.0047,0.9782,0.0319,0.0004</t>
+  </si>
+  <si>
+    <t>0.7440,0.0962,0.0373,0.0801</t>
+  </si>
+  <si>
+    <t>0.7884,0.0938,0.0746,0.0205</t>
+  </si>
+  <si>
+    <t>0.8418,0.2064,0.0028,0.0020</t>
+  </si>
+  <si>
+    <t>0.0254,0.9492,0.2683,0.0048</t>
+  </si>
+  <si>
+    <t>0.0355,0.8118,0.2760,0.0236</t>
+  </si>
+  <si>
+    <t>0.0414,0.0011,0.9641,0.0064</t>
+  </si>
+  <si>
+    <t>0.0145,0.0027,0.9894,0.0017</t>
+  </si>
+  <si>
+    <t>0.2385,0.0010,0.7882,0.0113</t>
+  </si>
+  <si>
+    <t>0.0492,0.0321,0.9662,0.0016</t>
+  </si>
+  <si>
+    <t>0.0171,0.9415,0.1443,0.0035</t>
+  </si>
+  <si>
+    <t>0.0087,0.0056,0.9892,0.0021</t>
+  </si>
+  <si>
+    <t>0.0262,0.6940,0.0064,0.8151</t>
+  </si>
+  <si>
+    <t>0.0103,0.9456,0.0091,0.0725</t>
+  </si>
+  <si>
+    <t>0.0009,0.9956,0.0024,0.0031</t>
+  </si>
+  <si>
+    <t>0.0005,0.9968,0.0089,0.0017</t>
+  </si>
+  <si>
+    <t>0.0032,0.0356,0.9801,0.0139</t>
+  </si>
+  <si>
+    <t>0.0023,0.0513,0.9911,0.0030</t>
+  </si>
+  <si>
+    <t>0.0693,0.0040,0.9638,0.0037</t>
+  </si>
+  <si>
+    <t>0.0214,0.0024,0.9856,0.0023</t>
+  </si>
+  <si>
+    <t>0.0031,0.0061,0.9942,0.0024</t>
+  </si>
+  <si>
+    <t>0.0084,0.0116,0.9819,0.0050</t>
+  </si>
+  <si>
+    <t>0.9825,0.0095,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9867,0.0008,0.0018,0.0052</t>
+  </si>
+  <si>
+    <t>0.8971,0.0810,0.0138,0.0136</t>
+  </si>
+  <si>
+    <t>0.0324,0.4183,0.9128,0.0144</t>
+  </si>
+  <si>
+    <t>0.9809,0.0100,0.0020,0.0040</t>
+  </si>
+  <si>
+    <t>0.9732,0.0306,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.8448,0.2180,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.9221,0.9532,0.0005</t>
+  </si>
+  <si>
+    <t>0.0081,0.3879,0.9513,0.0086</t>
+  </si>
+  <si>
+    <t>0.0431,0.2004,0.9136,0.0124</t>
+  </si>
+  <si>
+    <t>0.0004,0.9735,0.9682,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0057,0.9959,0.0007</t>
+  </si>
+  <si>
+    <t>0.1361,0.8485,0.0522,0.0018</t>
+  </si>
+  <si>
+    <t>0.0422,0.9555,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.9497,0.0075,0.0219,0.0128</t>
+  </si>
+  <si>
+    <t>0.4606,0.0553,0.6376,0.0208</t>
+  </si>
+  <si>
+    <t>0.0212,0.0364,0.9647,0.0265</t>
+  </si>
+  <si>
+    <t>0.0052,0.8871,0.8745,0.0013</t>
+  </si>
+  <si>
+    <t>0.0298,0.8412,0.6395,0.0071</t>
+  </si>
+  <si>
+    <t>0.0086,0.9797,0.0530,0.0015</t>
+  </si>
+  <si>
+    <t>0.0105,0.7963,0.7983,0.0025</t>
+  </si>
+  <si>
+    <t>0.0131,0.0031,0.0680,0.9665</t>
+  </si>
+  <si>
+    <t>0.0012,0.0022,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0046,0.0008,0.0011,0.9976</t>
+  </si>
+  <si>
+    <t>0.0294,0.0017,0.0058,0.9823</t>
+  </si>
+  <si>
+    <t>0.0029,0.0008,0.0006,0.9982</t>
+  </si>
+  <si>
+    <t>0.0007,0.0020,0.0008,0.9991</t>
+  </si>
+  <si>
+    <t>0.0021,0.9440,0.8579,0.0004</t>
+  </si>
+  <si>
+    <t>0.0125,0.5049,0.9469,0.0020</t>
+  </si>
+  <si>
+    <t>0.0209,0.1798,0.8793,0.0022</t>
+  </si>
+  <si>
+    <t>0.0232,0.5255,0.8478,0.0099</t>
+  </si>
+  <si>
+    <t>0.0004,0.9875,0.8637,0.0001</t>
+  </si>
+  <si>
+    <t>0.0167,0.7539,0.5678,0.0022</t>
+  </si>
+  <si>
+    <t>0.9957,0.0010,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9127,0.1600,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0063,0.0011,0.0029</t>
+  </si>
+  <si>
+    <t>0.9925,0.0019,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9521,0.0724,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9680,0.0103,0.0007,0.0054</t>
+  </si>
+  <si>
+    <t>0.9934,0.0025,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9878,0.0032,0.0006,0.0040</t>
+  </si>
+  <si>
+    <t>0.9942,0.0014,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9844,0.0071,0.0042,0.0029</t>
+  </si>
+  <si>
+    <t>0.9966,0.0003,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9831,0.0054,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.9916,0.0055,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9944,0.0032,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9924,0.0019,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.0030,0.0017,0.9957,0.0023</t>
+  </si>
+  <si>
+    <t>0.0627,0.0047,0.9725,0.0036</t>
+  </si>
+  <si>
+    <t>0.9120,0.0020,0.0199,0.0313</t>
+  </si>
+  <si>
+    <t>0.0083,0.0005,0.9944,0.0014</t>
+  </si>
+  <si>
+    <t>0.0265,0.9598,0.0012,0.0070</t>
+  </si>
+  <si>
+    <t>0.0016,0.9950,0.0018,0.0027</t>
+  </si>
+  <si>
+    <t>0.0110,0.9747,0.0033,0.0079</t>
+  </si>
+  <si>
+    <t>0.0024,0.9930,0.0018,0.0028</t>
+  </si>
+  <si>
+    <t>0.0006,0.9968,0.0024,0.0027</t>
+  </si>
+  <si>
+    <t>0.0027,0.9908,0.0019,0.0043</t>
+  </si>
+  <si>
+    <t>0.5536,0.5730,0.0068,0.0022</t>
+  </si>
+  <si>
+    <t>0.1932,0.6063,0.1531,0.0566</t>
+  </si>
+  <si>
+    <t>0.0885,0.0020,0.9758,0.0006</t>
+  </si>
+  <si>
+    <t>0.5315,0.0056,0.5395,0.0133</t>
+  </si>
+  <si>
+    <t>0.2966,0.0094,0.8077,0.0128</t>
+  </si>
+  <si>
+    <t>0.0182,0.0084,0.1222,0.9408</t>
+  </si>
+  <si>
+    <t>0.0012,0.9961,0.0138,0.0016</t>
+  </si>
+  <si>
+    <t>0.0010,0.9954,0.0056,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.9933,0.0015,0.0109</t>
+  </si>
+  <si>
+    <t>0.0106,0.9478,0.2306,0.0157</t>
+  </si>
+  <si>
+    <t>0.0136,0.9848,0.0103,0.0005</t>
+  </si>
+  <si>
+    <t>0.7465,0.2885,0.0440,0.0045</t>
+  </si>
+  <si>
+    <t>0.8217,0.1761,0.0071,0.0077</t>
+  </si>
+  <si>
+    <t>0.9959,0.0013,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9926,0.0007,0.0003,0.0038</t>
+  </si>
+  <si>
+    <t>0.9950,0.0005,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9858,0.0032,0.0025,0.0033</t>
+  </si>
+  <si>
+    <t>0.9935,0.0005,0.0001,0.0040</t>
+  </si>
+  <si>
+    <t>0.9907,0.0047,0.0018,0.0011</t>
+  </si>
+  <si>
+    <t>0.9877,0.0016,0.0007,0.0047</t>
+  </si>
+  <si>
+    <t>0.9913,0.0013,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.0016,0.8308,0.9576,0.0003</t>
+  </si>
+  <si>
+    <t>0.0146,0.8203,0.8210,0.0026</t>
+  </si>
+  <si>
+    <t>0.0024,0.4905,0.9633,0.0010</t>
+  </si>
+  <si>
+    <t>0.0886,0.0238,0.9199,0.0032</t>
+  </si>
+  <si>
+    <t>0.9601,0.0056,0.0280,0.0015</t>
+  </si>
+  <si>
+    <t>0.9426,0.0035,0.0580,0.0021</t>
+  </si>
+  <si>
+    <t>0.1891,0.0017,0.8982,0.0078</t>
+  </si>
+  <si>
+    <t>0.8510,0.0131,0.1377,0.0007</t>
+  </si>
+  <si>
+    <t>0.0166,0.0013,0.0126,0.9833</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0011,0.9992</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.0029,0.9990</t>
+  </si>
+  <si>
+    <t>0.0028,0.0004,0.0019,0.9975</t>
+  </si>
+  <si>
+    <t>0.0006,0.9488,0.8132,0.0029</t>
+  </si>
+  <si>
+    <t>0.9826,0.0044,0.0038,0.0039</t>
+  </si>
+  <si>
+    <t>0.0159,0.9651,0.0023,0.0348</t>
+  </si>
+  <si>
+    <t>0.9651,0.0132,0.0048,0.0141</t>
+  </si>
+  <si>
+    <t>0.5428,0.5497,0.0048,0.0062</t>
+  </si>
+  <si>
+    <t>0.9928,0.0010,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.4614,0.0049,0.0540,0.4985</t>
+  </si>
+  <si>
+    <t>0.9558,0.0121,0.0034,0.0140</t>
+  </si>
+  <si>
+    <t>0.0008,0.0724,0.9558,0.0768</t>
+  </si>
+  <si>
+    <t>0.7421,0.0002,0.0059,0.2179</t>
+  </si>
+  <si>
+    <t>0.9055,0.0086,0.0048,0.0725</t>
+  </si>
+  <si>
+    <t>0.1679,0.8128,0.0196,0.0216</t>
+  </si>
+  <si>
+    <t>0.4832,0.2449,0.0073,0.0776</t>
+  </si>
+  <si>
+    <t>0.9752,0.0071,0.0093,0.0022</t>
+  </si>
+  <si>
+    <t>0.4580,0.4805,0.0615,0.0412</t>
+  </si>
+  <si>
+    <t>0.9723,0.0040,0.0163,0.0011</t>
+  </si>
+  <si>
+    <t>0.9683,0.0255,0.0046,0.0018</t>
+  </si>
+  <si>
+    <t>0.9680,0.0060,0.0033,0.0122</t>
+  </si>
+  <si>
+    <t>0.9898,0.0019,0.0004,0.0039</t>
+  </si>
+  <si>
+    <t>0.9931,0.0012,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9929,0.0006,0.0003,0.0034</t>
+  </si>
+  <si>
+    <t>0.9932,0.0014,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9849,0.0073,0.0015,0.0029</t>
+  </si>
+  <si>
+    <t>0.9863,0.0050,0.0006,0.0043</t>
+  </si>
+  <si>
+    <t>0.9946,0.0003,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.8111,0.1660,0.0089,0.0095</t>
+  </si>
+  <si>
+    <t>0.4586,0.5657,0.0087,0.0088</t>
+  </si>
+  <si>
+    <t>0.6818,0.3894,0.0037,0.0025</t>
+  </si>
+  <si>
+    <t>0.9143,0.0868,0.0144,0.0039</t>
+  </si>
+  <si>
+    <t>0.9884,0.0074,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9817,0.0066,0.0023,0.0031</t>
+  </si>
+  <si>
+    <t>0.9849,0.0107,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0046,0.0004,0.0048</t>
+  </si>
+  <si>
+    <t>0.0090,0.0104,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.9579,0.0281,0.0058,0.0095</t>
+  </si>
+  <si>
+    <t>0.0007,0.0011,0.9943,0.0088</t>
+  </si>
+  <si>
+    <t>0.0144,0.0189,0.9715,0.0125</t>
+  </si>
+  <si>
+    <t>0.0195,0.0015,0.9916,0.0012</t>
+  </si>
+  <si>
+    <t>0.0225,0.1377,0.9483,0.0069</t>
+  </si>
+  <si>
+    <t>0.0044,0.0016,0.9963,0.0008</t>
+  </si>
+  <si>
+    <t>0.0084,0.0011,0.9929,0.0029</t>
+  </si>
+  <si>
+    <t>0.0028,0.0019,0.9963,0.0010</t>
+  </si>
+  <si>
+    <t>0.0679,0.0265,0.9202,0.0165</t>
+  </si>
+  <si>
+    <t>0.0662,0.0512,0.9245,0.0074</t>
+  </si>
+  <si>
+    <t>0.2091,0.0192,0.8653,0.0050</t>
+  </si>
+  <si>
+    <t>0.0629,0.5135,0.4922,0.0041</t>
+  </si>
+  <si>
+    <t>0.1077,0.0812,0.8526,0.0048</t>
+  </si>
+  <si>
+    <t>0.6929,0.0212,0.3469,0.0016</t>
+  </si>
+  <si>
+    <t>0.6403,0.1302,0.3017,0.0322</t>
+  </si>
+  <si>
+    <t>0.1385,0.0126,0.9094,0.0098</t>
+  </si>
+  <si>
+    <t>0.0048,0.9877,0.0009,0.0058</t>
+  </si>
+  <si>
+    <t>0.0022,0.9931,0.0013,0.0051</t>
+  </si>
+  <si>
+    <t>0.7597,0.3317,0.0092,0.0021</t>
+  </si>
+  <si>
+    <t>0.7154,0.3883,0.0025,0.0021</t>
+  </si>
+  <si>
+    <t>0.0283,0.9419,0.0016,0.0284</t>
+  </si>
+  <si>
+    <t>0.2408,0.0541,0.7552,0.0405</t>
+  </si>
+  <si>
+    <t>0.9460,0.0024,0.0544,0.0010</t>
+  </si>
+  <si>
+    <t>0.8886,0.0088,0.0434,0.0246</t>
+  </si>
+  <si>
+    <t>0.8731,0.0014,0.1991,0.0008</t>
+  </si>
+  <si>
+    <t>0.3086,0.0110,0.7932,0.0139</t>
+  </si>
+  <si>
+    <t>0.0026,0.0020,0.9753,0.0887</t>
+  </si>
+  <si>
+    <t>0.1777,0.0284,0.7687,0.0480</t>
+  </si>
+  <si>
+    <t>0.2848,0.0273,0.7895,0.0152</t>
+  </si>
+  <si>
+    <t>0.0132,0.0108,0.9764,0.0088</t>
+  </si>
+  <si>
+    <t>0.0627,0.2194,0.8215,0.0175</t>
+  </si>
+  <si>
+    <t>0.9882,0.0026,0.0003,0.0038</t>
+  </si>
+  <si>
+    <t>0.9897,0.0048,0.0007,0.0024</t>
+  </si>
+  <si>
+    <t>0.9708,0.0149,0.0005,0.0040</t>
+  </si>
+  <si>
+    <t>0.9803,0.0132,0.0019,0.0030</t>
+  </si>
+  <si>
+    <t>0.9875,0.0032,0.0006,0.0038</t>
+  </si>
+  <si>
+    <t>0.9891,0.0066,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9836,0.0089,0.0006,0.0036</t>
+  </si>
+  <si>
+    <t>0.9921,0.0023,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.0764,0.0035,0.9753,0.0021</t>
+  </si>
+  <si>
+    <t>0.2570,0.2014,0.6742,0.0366</t>
+  </si>
+  <si>
+    <t>0.7180,0.0301,0.1851,0.0303</t>
+  </si>
+  <si>
+    <t>0.0552,0.0037,0.9704,0.0021</t>
+  </si>
+  <si>
+    <t>0.0016,0.0011,0.9841,0.0356</t>
+  </si>
+  <si>
+    <t>0.0100,0.3587,0.8590,0.0085</t>
+  </si>
+  <si>
+    <t>0.0019,0.0022,0.9969,0.0013</t>
+  </si>
+  <si>
+    <t>0.0884,0.0041,0.9380,0.0178</t>
+  </si>
+  <si>
+    <t>0.0015,0.0027,0.9960,0.0024</t>
+  </si>
+  <si>
+    <t>0.0031,0.0051,0.9879,0.0149</t>
+  </si>
+  <si>
+    <t>0.0180,0.0054,0.9780,0.0033</t>
+  </si>
+  <si>
+    <t>0.4429,0.0205,0.6616,0.0231</t>
+  </si>
+  <si>
+    <t>0.9183,0.0094,0.0688,0.0055</t>
+  </si>
+  <si>
+    <t>0.9775,0.0011,0.0106,0.0015</t>
+  </si>
+  <si>
+    <t>0.9869,0.0070,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.9890,0.0036,0.0007,0.0024</t>
+  </si>
+  <si>
+    <t>0.9893,0.0050,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9841,0.0089,0.0023,0.0025</t>
+  </si>
+  <si>
+    <t>0.9920,0.0068,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9925,0.0019,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9936,0.0031,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9811,0.0140,0.0011,0.0017</t>
+  </si>
+  <si>
+    <t>0.0212,0.0851,0.9460,0.0068</t>
+  </si>
+  <si>
+    <t>0.0007,0.1566,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.0039,0.0078,0.9913,0.0044</t>
+  </si>
+  <si>
+    <t>0.0205,0.0143,0.9551,0.0090</t>
+  </si>
+  <si>
+    <t>0.0040,0.0040,0.9932,0.0024</t>
+  </si>
+  <si>
+    <t>0.1203,0.0012,0.1045,0.7284</t>
+  </si>
+  <si>
+    <t>0.0251,0.0009,0.9847,0.0050</t>
+  </si>
+  <si>
+    <t>0.2024,0.0994,0.6787,0.1241</t>
+  </si>
+  <si>
+    <t>0.4392,0.0005,0.0035,0.6898</t>
+  </si>
+  <si>
+    <t>0.0159,0.0130,0.0009,0.9901</t>
+  </si>
+  <si>
+    <t>0.0281,0.0006,0.0060,0.9811</t>
+  </si>
+  <si>
+    <t>0.0021,0.0005,0.0016,0.9980</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.8528,0.0183,0.0880,0.0259</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,10 +2208,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3552,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,10 +5134,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
